--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484213_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484213_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4765</v>
+        <v>1.2203</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0912</v>
+        <v>2.8078</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6147</v>
+        <v>-1.5875</v>
       </c>
       <c r="G2" t="n">
         <v>-0.7963</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2899</v>
+        <v>-0.5461</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2726</v>
+        <v>-0.0108</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5624</v>
+        <v>-0.5352</v>
       </c>
       <c r="V2" t="n">
         <v>0.6093</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. VASCENCO BADRAJAN</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5273</v>
+        <v>0.2485</v>
       </c>
       <c r="E3" t="n">
-        <v>1.341</v>
+        <v>0.7917</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8137</v>
+        <v>-0.5432</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8199</v>
+        <v>-0.797</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5152</v>
+        <v>-0.945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3352</v>
+        <v>0.148</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9695</v>
+        <v>0.771</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3083</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6613</v>
+        <v>0.6879</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1496</v>
+        <v>-1.568</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8235</v>
+        <v>-1.0281</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.5399</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2108</v>
+        <v>-0.1266</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3715</v>
+        <v>0.0207</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5823</v>
+        <v>-0.1472</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>N. VASCENCO BADRAJAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.013</v>
+        <v>0.121</v>
       </c>
       <c r="E4" t="n">
-        <v>0.529</v>
+        <v>1.0982</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.516</v>
+        <v>-0.9772</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.797</v>
+        <v>0.8199</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.945</v>
+        <v>-0.5152</v>
       </c>
       <c r="I4" t="n">
-        <v>0.148</v>
+        <v>1.3352</v>
       </c>
       <c r="J4" t="n">
-        <v>0.771</v>
+        <v>0.9695</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.3083</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6879</v>
+        <v>0.6613</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.568</v>
+        <v>-0.1496</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0281</v>
+        <v>-0.8235</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5399</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3621</v>
+        <v>-0.617</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2421</v>
+        <v>0.1287</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.12</v>
+        <v>-0.7457</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0406</v>
+        <v>-0.4922</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3476</v>
+        <v>-0.0442</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6931</v>
+        <v>-0.448</v>
       </c>
       <c r="G5" t="n">
         <v>1.0656</v>
@@ -844,13 +844,13 @@
         <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.669</v>
+        <v>-1.1205</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4842</v>
+        <v>-0.1808</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1848</v>
+        <v>-0.9397</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2186</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.9826</v>
+        <v>-2.7063</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8506</v>
+        <v>-0.2117</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.132</v>
+        <v>-2.4945</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8282</v>
+        <v>-0.361</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8961</v>
+        <v>-0.9678</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0679</v>
+        <v>0.6068</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3128</v>
+        <v>1.9011</v>
       </c>
       <c r="K6" t="n">
-        <v>0.165</v>
+        <v>0.6191</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1478</v>
+        <v>1.2821</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.1411</v>
+        <v>-2.2621</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0611</v>
+        <v>-1.5868</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0799</v>
+        <v>-0.6753</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
         <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8576</v>
+        <v>-1.5173</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5226</v>
+        <v>-0.1594</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3351</v>
+        <v>-1.3579</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6642</v>
+        <v>-1.2186</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.024</v>
+        <v>-2.9216</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3933</v>
+        <v>-0.8713</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6307</v>
+        <v>-2.0503</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.361</v>
+        <v>-1.8282</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9678</v>
+        <v>-1.8961</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6068</v>
+        <v>0.0679</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9011</v>
+        <v>1.3128</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6191</v>
+        <v>0.165</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2821</v>
+        <v>1.1478</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2621</v>
+        <v>-3.1411</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5868</v>
+        <v>-2.0611</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6753</v>
+        <v>-1.0799</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
         <v>2.3441</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8351</v>
+        <v>-1.7966</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.341</v>
+        <v>-0.5432</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4941</v>
+        <v>-1.2533</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3044</v>
+        <v>-2.9327</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5209</v>
+        <v>-2.2582</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7835</v>
+        <v>-0.6745</v>
       </c>
       <c r="G8" t="n">
         <v>2.3855</v>
@@ -1078,13 +1078,13 @@
         <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9784</v>
+        <v>-0.6067</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2421</v>
+        <v>0.0207</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7363</v>
+        <v>-0.6274</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6093</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.8305</v>
+        <v>-7.083</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4046</v>
+        <v>-2.3847</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.4259</v>
+        <v>-4.6983</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7211</v>
@@ -1156,13 +1156,13 @@
         <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1996</v>
+        <v>-1.452</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1649</v>
+        <v>-0.1449</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0347</v>
+        <v>-1.3071</v>
       </c>
       <c r="V9" t="n">
         <v>-3.3238</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.132400000000001</v>
+        <v>-8.409800000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4344</v>
+        <v>-5.6573</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.698</v>
+        <v>-2.7524</v>
       </c>
       <c r="G10" t="n">
         <v>-5.2252</v>
@@ -1234,13 +1234,13 @@
         <v>3.3208</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5248</v>
+        <v>-1.8021</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.03</v>
+        <v>-0.2529</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4947</v>
+        <v>-1.5492</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7731</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.624000000000001</v>
+        <v>-8.755800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.3322</v>
+        <v>-6.3823</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2918</v>
+        <v>-2.3735</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0766</v>
@@ -1312,13 +1312,13 @@
         <v>3.3208</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3986</v>
+        <v>-1.5304</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5598</v>
+        <v>-0.6099</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8388</v>
+        <v>-0.9205</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6093</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-32.9217</v>
+        <v>-31.7116</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.3224</v>
+        <v>-13.112</v>
       </c>
       <c r="F12" t="n">
         <v>-18.5994</v>
@@ -1390,13 +1390,13 @@
         <v>18.5575</v>
       </c>
       <c r="S12" t="n">
-        <v>-12.3259</v>
+        <v>-11.1153</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.9426</v>
+        <v>-1.7318</v>
       </c>
       <c r="U12" t="n">
-        <v>-9.383199999999999</v>
+        <v>-9.3832</v>
       </c>
       <c r="V12" t="n">
         <v>-9.084799999999998</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.145</v>
+        <v>8.7401</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1637</v>
+        <v>4.5682</v>
       </c>
       <c r="F13" t="n">
-        <v>3.9813</v>
+        <v>4.1719</v>
       </c>
       <c r="G13" t="n">
         <v>1.2251</v>
@@ -1468,13 +1468,13 @@
         <v>2.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5645</v>
+        <v>1.1596</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6219</v>
+        <v>1.0264</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0574</v>
+        <v>0.1333</v>
       </c>
       <c r="V13" t="n">
         <v>4.5973</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.7433</v>
+        <v>6.7044</v>
       </c>
       <c r="E14" t="n">
-        <v>7.1249</v>
+        <v>2.734</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6183</v>
+        <v>3.9704</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1072</v>
+        <v>5.2221</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4823</v>
+        <v>3.4562</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.375</v>
+        <v>1.7659</v>
       </c>
       <c r="J14" t="n">
-        <v>3.639</v>
+        <v>3.9684</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6646</v>
+        <v>3.6851</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0257</v>
+        <v>0.2833</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5318</v>
+        <v>1.2537</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1824</v>
+        <v>-0.2289</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3494</v>
+        <v>1.4826</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
         <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8547</v>
+        <v>1.1232</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4394</v>
+        <v>1.1413</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4153</v>
+        <v>-0.0181</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9492</v>
+        <v>6.4625</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4418</v>
+        <v>5.7093</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5074</v>
+        <v>0.7532</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2221</v>
+        <v>1.1072</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4562</v>
+        <v>2.4823</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7659</v>
+        <v>-1.375</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9684</v>
+        <v>3.639</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6851</v>
+        <v>3.6646</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2833</v>
+        <v>-0.0257</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2537</v>
+        <v>-2.5318</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2289</v>
+        <v>-1.1824</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4826</v>
+        <v>-1.3494</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
         <v>2.7348</v>
       </c>
       <c r="S15" t="n">
-        <v>1.368</v>
+        <v>2.5739</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8491</v>
+        <v>2.0238</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4811</v>
+        <v>0.5501</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.2286</v>
+        <v>6.4257</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9529</v>
+        <v>3.8518</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2757</v>
+        <v>2.5739</v>
       </c>
       <c r="G16" t="n">
         <v>5.8034</v>
@@ -1702,13 +1702,13 @@
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5506</v>
+        <v>1.7478</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2355</v>
+        <v>1.1344</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3151</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>1.2186</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7329</v>
+        <v>4.4563</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4022</v>
+        <v>3.9078</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3307</v>
+        <v>0.5485</v>
       </c>
       <c r="G17" t="n">
         <v>1.7882</v>
@@ -1780,13 +1780,13 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3819</v>
+        <v>1.1054</v>
       </c>
       <c r="T17" t="n">
-        <v>0.311</v>
+        <v>0.8165</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.2888</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1292</v>
+        <v>1.8241</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9304</v>
+        <v>1.436</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1988</v>
+        <v>0.3881</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0516</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.7036</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1816</v>
+        <v>0.324</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1903</v>
+        <v>0.3796</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6835</v>
+        <v>0.6368</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8008</v>
+        <v>0.6997</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1173</v>
+        <v>-0.0629</v>
       </c>
       <c r="G19" t="n">
         <v>0.0336</v>
@@ -1936,13 +1936,13 @@
         <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2592</v>
+        <v>0.2126</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4925</v>
+        <v>0.3914</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2041</v>
+        <v>0.5152</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8120000000000001</v>
+        <v>-1.3274</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0161</v>
+        <v>1.8426</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3554</v>
+        <v>-0.5508</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8813</v>
+        <v>0.272</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5259</v>
+        <v>-0.8227</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4172</v>
+        <v>0.5627</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0819</v>
+        <v>1.2497</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3354</v>
+        <v>-0.6869</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7727</v>
+        <v>-1.1135</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.9777</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8095</v>
+        <v>-0.1358</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-4.1022</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.542</v>
+        <v>1.3282</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3715</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1705</v>
+        <v>0.612</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4092</v>
+        <v>-0.1044</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0352</v>
+        <v>0.9131</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6261</v>
+        <v>-1.0175</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5508</v>
+        <v>-0.3554</v>
       </c>
       <c r="H21" t="n">
-        <v>0.272</v>
+        <v>-0.8813</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8227</v>
+        <v>0.5259</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5627</v>
+        <v>1.4172</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2497</v>
+        <v>0.0819</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6869</v>
+        <v>1.3354</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1135</v>
+        <v>-1.7727</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9777</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1358</v>
+        <v>-0.8095</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1022</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4038</v>
+        <v>0.6418</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0083</v>
+        <v>0.4726</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3955</v>
+        <v>0.1691</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0764</v>
+        <v>-2.0647</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.994</v>
+        <v>-3.8929</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9176</v>
+        <v>1.8282</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6872</v>
@@ -2170,13 +2170,13 @@
         <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3922</v>
+        <v>2.4039</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2355</v>
+        <v>1.3366</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1567</v>
+        <v>1.0673</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>32.922</v>
+        <v>33.596</v>
       </c>
       <c r="E23" t="n">
-        <v>18.5995</v>
+        <v>18.5996</v>
       </c>
       <c r="F23" t="n">
-        <v>14.3225</v>
+        <v>14.9964</v>
       </c>
       <c r="G23" t="n">
         <v>10.5346</v>
@@ -2218,7 +2218,7 @@
         <v>10.5336</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001100000000000101</v>
+        <v>0.001099999999999879</v>
       </c>
       <c r="J23" t="n">
         <v>17.5252</v>
@@ -2227,7 +2227,7 @@
         <v>16.8432</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6821000000000002</v>
+        <v>0.6821000000000006</v>
       </c>
       <c r="M23" t="n">
         <v>-6.9907</v>
@@ -2236,10 +2236,10 @@
         <v>-6.3096</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6809000000000001</v>
+        <v>-0.6808999999999998</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767</v>
+        <v>0.9766999999999996</v>
       </c>
       <c r="Q23" t="n">
         <v>-18.5576</v>
@@ -2248,13 +2248,13 @@
         <v>19.5343</v>
       </c>
       <c r="S23" t="n">
-        <v>12.3257</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>9.383100000000001</v>
+        <v>9.3832</v>
       </c>
       <c r="U23" t="n">
-        <v>2.9426</v>
+        <v>3.6166</v>
       </c>
       <c r="V23" t="n">
         <v>9.084899999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484213_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484213_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2203</v>
+        <v>1.221</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8078</v>
+        <v>1.221</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5875</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7963</v>
+        <v>1.221</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.052</v>
+        <v>0.614</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2556</v>
+        <v>0.607</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6</v>
+        <v>1.221</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4786</v>
+        <v>0.614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1214</v>
+        <v>0.607</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3964</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.5306</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1342</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5461</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0108</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5352</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2485</v>
+        <v>1.2203</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7917</v>
+        <v>2.8078</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5432</v>
+        <v>-1.5875</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.797</v>
+        <v>-0.7963</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.945</v>
+        <v>-1.052</v>
       </c>
       <c r="I3" t="n">
-        <v>0.148</v>
+        <v>0.2556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.771</v>
+        <v>1.6</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08309999999999999</v>
+        <v>1.4786</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6879</v>
+        <v>0.1214</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.568</v>
+        <v>-2.3964</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0281</v>
+        <v>-2.5306</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5399</v>
+        <v>0.1342</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1266</v>
+        <v>-0.5461</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0207</v>
+        <v>-0.0108</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1472</v>
+        <v>-0.5352</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. VASCENCO BADRAJAN</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.121</v>
+        <v>0.2485</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0982</v>
+        <v>0.7917</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9772</v>
+        <v>-0.5432</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8199</v>
+        <v>-0.797</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5152</v>
+        <v>-0.945</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3352</v>
+        <v>0.148</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9695</v>
+        <v>0.771</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3083</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6613</v>
+        <v>0.6879</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1496</v>
+        <v>-1.568</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8235</v>
+        <v>-1.0281</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.5399</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.617</v>
+        <v>-0.1266</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1287</v>
+        <v>0.0207</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7457</v>
+        <v>-0.1472</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>N. VASCENCO BADRAJAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4922</v>
+        <v>0.121</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0442</v>
+        <v>1.0982</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.448</v>
+        <v>-0.9772</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0656</v>
+        <v>0.8199</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0266</v>
+        <v>-0.5152</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0922</v>
+        <v>1.3352</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1366</v>
+        <v>0.9695</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1228</v>
+        <v>0.3083</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0138</v>
+        <v>0.6613</v>
       </c>
       <c r="M5" t="n">
-        <v>0.929</v>
+        <v>-0.1496</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1494</v>
+        <v>-0.8235</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0784</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1205</v>
+        <v>-0.617</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1808</v>
+        <v>0.1287</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9397</v>
+        <v>-0.7457</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7063</v>
+        <v>-0.4922</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2117</v>
+        <v>-0.0442</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4945</v>
+        <v>-0.448</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.361</v>
+        <v>1.0656</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9678</v>
+        <v>-0.0266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6068</v>
+        <v>1.0922</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9011</v>
+        <v>0.1366</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6191</v>
+        <v>0.1228</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2821</v>
+        <v>0.0138</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2621</v>
+        <v>0.929</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5868</v>
+        <v>-0.1494</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6753</v>
+        <v>1.0784</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5173</v>
+        <v>-1.1205</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1594</v>
+        <v>-0.1808</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3579</v>
+        <v>-0.9397</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2186</v>
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.083</v>
+        <v>-3.9273</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3847</v>
+        <v>-1.4327</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.6983</v>
+        <v>-2.4945</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7211</v>
+        <v>-1.582</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6524</v>
+        <v>-1.5818</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3735</v>
+        <v>-0.0002</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.6802</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7232</v>
+        <v>0.0051</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.6421</v>
+        <v>0.6751</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8022</v>
+        <v>-2.2621</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0708</v>
+        <v>-1.5868</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2687</v>
+        <v>-0.6753</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
         <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.452</v>
+        <v>-1.5173</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1449</v>
+        <v>-0.1594</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3071</v>
+        <v>-1.3579</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.3238</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.9331</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.409800000000001</v>
+        <v>-7.083</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6573</v>
+        <v>-2.3847</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7524</v>
+        <v>-4.6983</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.2252</v>
+        <v>-1.7211</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.2021</v>
+        <v>0.6524</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0231</v>
+        <v>-2.3735</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4742</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5872000000000001</v>
+        <v>2.7232</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8871</v>
+        <v>-2.6421</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.751</v>
+        <v>-1.8022</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.615</v>
+        <v>-2.0708</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.136</v>
+        <v>0.2687</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3208</v>
+        <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8021</v>
+        <v>-1.452</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2529</v>
+        <v>-0.1449</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5492</v>
+        <v>-1.3071</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7731</v>
+        <v>-3.3238</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7731</v>
+        <v>-3.9331</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.755800000000001</v>
+        <v>-8.409800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3823</v>
+        <v>-5.6573</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3735</v>
+        <v>-2.7524</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.0766</v>
+        <v>-5.2252</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9975</v>
+        <v>-3.2021</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0792</v>
+        <v>-2.0231</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08790000000000001</v>
+        <v>-2.4742</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08690000000000001</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001</v>
+        <v>-1.8871</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.1646</v>
+        <v>-2.751</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.0844</v>
+        <v>-2.615</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0801</v>
+        <v>-0.136</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.5395</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.8603</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
         <v>3.3208</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5304</v>
+        <v>-1.8021</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6099</v>
+        <v>-0.2529</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9205</v>
+        <v>-1.5492</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093</v>
+        <v>-1.7731</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6093</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-31.7116</v>
+        <v>-8.755800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.112</v>
+        <v>-6.3823</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.5994</v>
+        <v>-2.3735</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.5344</v>
+        <v>-4.0766</v>
       </c>
       <c r="H12" t="n">
-        <v>-10.5334</v>
+        <v>-2.9975</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.001099999999999879</v>
+        <v>-1.0792</v>
       </c>
       <c r="J12" t="n">
-        <v>6.9905</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>6.3096</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6809999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.5252</v>
+        <v>-4.1646</v>
       </c>
       <c r="N12" t="n">
-        <v>-16.843</v>
+        <v>-3.0844</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6819000000000001</v>
+        <v>-1.0801</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9767000000000003</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q12" t="n">
-        <v>-19.5342</v>
+        <v>-5.8603</v>
       </c>
       <c r="R12" t="n">
-        <v>18.5575</v>
+        <v>3.3208</v>
       </c>
       <c r="S12" t="n">
-        <v>-11.1153</v>
+        <v>-1.5304</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7318</v>
+        <v>-0.6099</v>
       </c>
       <c r="U12" t="n">
-        <v>-9.3832</v>
+        <v>-0.9205</v>
       </c>
       <c r="V12" t="n">
-        <v>-9.084799999999998</v>
+        <v>-0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1637</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.2485</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>CB ANDRATX</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.7401</v>
+        <v>-31.7116</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5682</v>
+        <v>-13.112</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1719</v>
+        <v>-18.5994</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2251</v>
+        <v>-10.5344</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0875</v>
+        <v>-10.5334</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.001099999999999435</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1714</v>
+        <v>6.9906</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1118</v>
+        <v>6.309600000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9404</v>
+        <v>0.6809999999999991</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0537</v>
+        <v>-17.5252</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0243</v>
+        <v>-16.843</v>
       </c>
       <c r="O13" t="n">
-        <v>1.078</v>
+        <v>-0.6819000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7581</v>
+        <v>-0.9766999999999995</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1721</v>
+        <v>-19.5342</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9301</v>
+        <v>18.5575</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1596</v>
+        <v>-11.1153</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0264</v>
+        <v>-1.7318</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1333</v>
+        <v>-9.383200000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5973</v>
+        <v>-9.0848</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5424</v>
+        <v>1.1637</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0549</v>
-      </c>
+        <v>-10.2485</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7044</v>
+        <v>8.7401</v>
       </c>
       <c r="E14" t="n">
-        <v>2.734</v>
+        <v>4.5682</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9704</v>
+        <v>4.1719</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2221</v>
+        <v>1.2251</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4562</v>
+        <v>2.0875</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7659</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9684</v>
+        <v>0.1714</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6851</v>
+        <v>2.1118</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2833</v>
+        <v>-1.9404</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2537</v>
+        <v>1.0537</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2289</v>
+        <v>-0.0243</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4826</v>
+        <v>1.078</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7348</v>
+        <v>2.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1232</v>
+        <v>1.1596</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1413</v>
+        <v>1.0264</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0181</v>
+        <v>0.1333</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5545</v>
+        <v>4.5973</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>4.5424</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1645,72 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4625</v>
+        <v>6.7044</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7093</v>
+        <v>2.734</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7532</v>
+        <v>3.9704</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1072</v>
+        <v>5.2221</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4823</v>
+        <v>3.4562</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.375</v>
+        <v>1.7659</v>
       </c>
       <c r="J15" t="n">
-        <v>3.639</v>
+        <v>3.9684</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6646</v>
+        <v>3.6851</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0257</v>
+        <v>0.2833</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5318</v>
+        <v>1.2537</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1824</v>
+        <v>-0.2289</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3494</v>
+        <v>1.4826</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
         <v>2.7348</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5739</v>
+        <v>1.1232</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0238</v>
+        <v>1.1413</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5501</v>
+        <v>-0.0181</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1719,11 +1790,16 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4563</v>
+        <v>6.1555</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9078</v>
+        <v>5.4023</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5485</v>
+        <v>0.7532</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7882</v>
+        <v>0.8002</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2239</v>
+        <v>2.1753</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5643</v>
+        <v>-1.375</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2866</v>
+        <v>3.332</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7776999999999999</v>
+        <v>3.3576</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5089</v>
+        <v>-0.0257</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4984</v>
+        <v>-2.5318</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5538</v>
+        <v>-1.1824</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9445</v>
+        <v>-1.3494</v>
       </c>
       <c r="P17" t="n">
         <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>2.7348</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1054</v>
+        <v>2.5739</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8165</v>
+        <v>2.0238</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2888</v>
+        <v>0.5501</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8241</v>
+        <v>4.4563</v>
       </c>
       <c r="E18" t="n">
-        <v>1.436</v>
+        <v>3.9078</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3881</v>
+        <v>0.5485</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0516</v>
+        <v>1.7882</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1371</v>
+        <v>0.2239</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1887</v>
+        <v>1.5643</v>
       </c>
       <c r="J18" t="n">
-        <v>1.112</v>
+        <v>3.2866</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4912</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6208</v>
+        <v>2.5089</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1636</v>
+        <v>-1.4984</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.354</v>
+        <v>-0.5538</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8095</v>
+        <v>-0.9445</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7036</v>
+        <v>1.1054</v>
       </c>
       <c r="T18" t="n">
-        <v>0.324</v>
+        <v>0.8165</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3796</v>
+        <v>0.2888</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. TALTAVULL BALLE</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6368</v>
+        <v>1.8241</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6997</v>
+        <v>1.436</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0629</v>
+        <v>0.3881</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0336</v>
+        <v>-0.0516</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8427</v>
+        <v>0.1371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8091</v>
+        <v>-0.1887</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3083</v>
+        <v>1.112</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.4912</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6741</v>
+        <v>0.6208</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2747</v>
+        <v>-1.1636</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1397</v>
+        <v>-0.354</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.135</v>
+        <v>-0.8095</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2126</v>
+        <v>0.7036</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3914</v>
+        <v>0.324</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1789</v>
+        <v>0.3796</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>P. TALTAVULL BALLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5152</v>
+        <v>0.6368</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3274</v>
+        <v>0.6997</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8426</v>
+        <v>-0.0629</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5508</v>
+        <v>0.0336</v>
       </c>
       <c r="H20" t="n">
-        <v>0.272</v>
+        <v>0.8427</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8227</v>
+        <v>-0.8091</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5627</v>
+        <v>0.3083</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2497</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6869</v>
+        <v>-0.6741</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1135</v>
+        <v>-0.2747</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9777</v>
+        <v>-0.1397</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1358</v>
+        <v>-0.135</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3441</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3282</v>
+        <v>0.2126</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.3914</v>
       </c>
       <c r="U20" t="n">
-        <v>0.612</v>
+        <v>-0.1789</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1044</v>
+        <v>0.5152</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9131</v>
+        <v>-1.3274</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0175</v>
+        <v>1.8426</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3554</v>
+        <v>-0.5508</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8813</v>
+        <v>0.272</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5259</v>
+        <v>-0.8227</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4172</v>
+        <v>0.5627</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0819</v>
+        <v>1.2497</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3354</v>
+        <v>-0.6869</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7727</v>
+        <v>-1.1135</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.9777</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8095</v>
+        <v>-0.1358</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-4.1022</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6418</v>
+        <v>1.3282</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4726</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1691</v>
+        <v>0.612</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0647</v>
+        <v>0.307</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8929</v>
+        <v>0.307</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8282</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.6872</v>
+        <v>0.307</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2449</v>
+        <v>0.307</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4424</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.3227</v>
+        <v>0.307</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3419</v>
+        <v>0.307</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9808</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3645</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.903</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5385</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4039</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3366</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0673</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-0.1044</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9131</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.0175</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.3554</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.8813</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5259</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.4172</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.3354</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.7727</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.9631999999999999</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.8095</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.6418</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>J. GASCON TORNE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.0647</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.8929</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.8282</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-3.6872</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.2449</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.4424</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.3227</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.3419</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.9808</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.3645</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.903</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.4039</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.3366</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.0673</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484213_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>33.596</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>18.5996</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>14.9964</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>10.5346</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>10.5336</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>0.001099999999999879</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>17.5252</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>16.8432</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>0.6821000000000006</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>-6.9907</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-6.3096</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>-0.6808999999999998</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>0.9766999999999996</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-18.5576</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>19.5343</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>13</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>9.3832</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>3.6166</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V25" t="n">
         <v>9.084899999999999</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W25" t="n">
         <v>10.2486</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X25" t="n">
         <v>-1.1637</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
